--- a/middle_dir/GH_collect_output_here.xlsx
+++ b/middle_dir/GH_collect_output_here.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghausm\Desktop\SarahConnor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielagaio/github/metadata_mining/middle_dir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92A361C2-4E7F-4886-AD07-9C358128EF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAB40EB8-BD2C-9C4E-A18C-7919AAD2BA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="0" windowWidth="22944" windowHeight="12360" xr2:uid="{81E6816F-E096-F749-BDE3-6555DF2B5DD6}"/>
+    <workbookView xWindow="1800" yWindow="780" windowWidth="27000" windowHeight="15640" xr2:uid="{81E6816F-E096-F749-BDE3-6555DF2B5DD6}"/>
   </bookViews>
   <sheets>
     <sheet name="samples.ordered" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="989">
   <si>
     <t>SRS2862295</t>
   </si>
@@ -2984,6 +2984,9 @@
   </si>
   <si>
     <t>hydroponic potato-crop water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes it should have been animal </t>
   </si>
 </sst>
 </file>
@@ -3140,7 +3143,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3332,6 +3335,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -3493,7 +3508,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3502,6 +3517,8 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3877,18 +3894,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{513ADDCC-8420-914D-BF06-F1BE1EB49DA2}">
-  <dimension ref="A1:G251"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:H251"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.1484375" customWidth="1"/>
-    <col min="2" max="2" width="8.34765625" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="54.84765625" customWidth="1"/>
-    <col min="5" max="5" width="31.1484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.83203125" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>250</v>
       </c>
@@ -3908,7 +3925,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>198</v>
       </c>
@@ -3928,7 +3945,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>93</v>
       </c>
@@ -3948,7 +3965,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>202</v>
       </c>
@@ -3968,7 +3985,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -3988,7 +4005,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>129</v>
       </c>
@@ -4008,7 +4025,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4028,7 +4045,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>180</v>
       </c>
@@ -4048,7 +4065,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>169</v>
       </c>
@@ -4068,7 +4085,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
@@ -4088,7 +4105,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>216</v>
       </c>
@@ -4108,7 +4125,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>91</v>
       </c>
@@ -4129,7 +4146,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>90</v>
       </c>
@@ -4150,7 +4167,7 @@
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>210</v>
       </c>
@@ -4170,7 +4187,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>77</v>
       </c>
@@ -4190,7 +4207,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>123</v>
       </c>
@@ -4210,7 +4227,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>54</v>
       </c>
@@ -4230,7 +4247,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
@@ -4250,7 +4267,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>241</v>
       </c>
@@ -4270,7 +4287,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
@@ -4290,7 +4307,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -4310,7 +4327,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -4330,7 +4347,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -4350,7 +4367,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>186</v>
       </c>
@@ -4370,7 +4387,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -4390,7 +4407,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -4410,7 +4427,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>203</v>
       </c>
@@ -4430,7 +4447,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>149</v>
       </c>
@@ -4450,7 +4467,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -4470,7 +4487,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>152</v>
       </c>
@@ -4490,24 +4507,28 @@
         <v>327</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A31" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F31" t="s">
+      <c r="E31" s="7"/>
+      <c r="F31" s="7" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="G31" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -4527,7 +4548,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -4547,7 +4568,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -4567,7 +4588,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>100</v>
       </c>
@@ -4587,27 +4608,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A36" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="7" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="G36" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>86</v>
       </c>
@@ -4627,7 +4651,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>226</v>
       </c>
@@ -4647,7 +4671,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -4667,7 +4691,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -4687,7 +4711,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -4707,27 +4731,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A42" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="F42" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F42" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -4747,27 +4774,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A44" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="F44" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F44" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>233</v>
       </c>
@@ -4787,7 +4817,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>18</v>
       </c>
@@ -4807,7 +4837,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>146</v>
       </c>
@@ -4827,7 +4857,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -4847,7 +4877,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>133</v>
       </c>
@@ -4867,27 +4897,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A50" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="F50" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F50" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -4907,7 +4940,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>88</v>
       </c>
@@ -4927,7 +4960,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -4947,7 +4980,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -4967,7 +5000,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -4987,7 +5020,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>183</v>
       </c>
@@ -5007,7 +5040,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>244</v>
       </c>
@@ -5027,27 +5060,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A58" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="6" t="s">
         <v>760</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="F58" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F58" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>89</v>
       </c>
@@ -5067,7 +5103,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>126</v>
       </c>
@@ -5087,7 +5123,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -5107,7 +5143,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>134</v>
       </c>
@@ -5127,47 +5163,53 @@
         <v>257</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A63" t="s">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="F63" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A64" t="s">
+      <c r="F63" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="F64" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F64" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>204</v>
       </c>
@@ -5187,27 +5229,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A66" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="F66" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F66" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -5227,7 +5272,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -5247,7 +5292,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>99</v>
       </c>
@@ -5267,7 +5312,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -5287,7 +5332,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>191</v>
       </c>
@@ -5307,7 +5352,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>211</v>
       </c>
@@ -5327,7 +5372,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>138</v>
       </c>
@@ -5347,7 +5392,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>209</v>
       </c>
@@ -5367,7 +5412,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -5387,7 +5432,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>247</v>
       </c>
@@ -5407,7 +5452,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>231</v>
       </c>
@@ -5427,7 +5472,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>124</v>
       </c>
@@ -5447,7 +5492,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>205</v>
       </c>
@@ -5467,7 +5512,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>32</v>
       </c>
@@ -5487,7 +5532,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>73</v>
       </c>
@@ -5507,7 +5552,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -5527,7 +5572,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>53</v>
       </c>
@@ -5547,7 +5592,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>234</v>
       </c>
@@ -5567,7 +5612,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -5587,7 +5632,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>3</v>
       </c>
@@ -5607,7 +5652,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>137</v>
       </c>
@@ -5627,7 +5672,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -5647,7 +5692,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>142</v>
       </c>
@@ -5667,7 +5712,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>1</v>
       </c>
@@ -5687,7 +5732,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>111</v>
       </c>
@@ -5707,7 +5752,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>71</v>
       </c>
@@ -5727,7 +5772,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>63</v>
       </c>
@@ -5747,7 +5792,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>74</v>
       </c>
@@ -5767,7 +5812,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>112</v>
       </c>
@@ -5787,7 +5832,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>132</v>
       </c>
@@ -5807,67 +5852,76 @@
         <v>257</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A97" t="s">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A98" t="s">
+      <c r="G97" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="6" t="s">
         <v>579</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A99" t="s">
+      <c r="G98" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="6" t="s">
         <v>583</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="G99" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>130</v>
       </c>
@@ -5887,7 +5941,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>193</v>
       </c>
@@ -5907,7 +5961,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -5927,7 +5981,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>246</v>
       </c>
@@ -5947,7 +6001,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>162</v>
       </c>
@@ -5967,7 +6021,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>65</v>
       </c>
@@ -5987,7 +6041,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -6007,7 +6061,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -6027,7 +6081,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>80</v>
       </c>
@@ -6047,7 +6101,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>120</v>
       </c>
@@ -6067,7 +6121,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>102</v>
       </c>
@@ -6087,7 +6141,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>173</v>
       </c>
@@ -6107,7 +6161,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>38</v>
       </c>
@@ -6127,7 +6181,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>236</v>
       </c>
@@ -6147,7 +6201,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>60</v>
       </c>
@@ -6167,7 +6221,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>219</v>
       </c>
@@ -6187,7 +6241,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>223</v>
       </c>
@@ -6207,7 +6261,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -6227,7 +6281,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -6247,7 +6301,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>103</v>
       </c>
@@ -6267,7 +6321,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>27</v>
       </c>
@@ -6287,7 +6341,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>201</v>
       </c>
@@ -6307,7 +6361,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>194</v>
       </c>
@@ -6327,27 +6381,33 @@
         <v>257</v>
       </c>
     </row>
-    <row r="123" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A123" s="5" t="s">
+    <row r="123" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B123" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="C123" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="D123" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="E123" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F123" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F123" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>113</v>
       </c>
@@ -6367,27 +6427,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A125" t="s">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="F125" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F125" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>148</v>
       </c>
@@ -6407,7 +6470,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>212</v>
       </c>
@@ -6427,7 +6490,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>35</v>
       </c>
@@ -6447,7 +6510,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>109</v>
       </c>
@@ -6467,7 +6530,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>117</v>
       </c>
@@ -6487,7 +6550,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -6507,7 +6570,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>0</v>
       </c>
@@ -6527,7 +6590,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>176</v>
       </c>
@@ -6547,7 +6610,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>49</v>
       </c>
@@ -6567,7 +6630,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>143</v>
       </c>
@@ -6587,7 +6650,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>12</v>
       </c>
@@ -6607,47 +6670,53 @@
         <v>306</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A137" t="s">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="F137" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A138" t="s">
+      <c r="F137" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="6" t="s">
         <v>693</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="6" t="s">
         <v>694</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="6" t="s">
         <v>695</v>
       </c>
-      <c r="F138" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F138" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>238</v>
       </c>
@@ -6667,7 +6736,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>104</v>
       </c>
@@ -6687,7 +6756,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>41</v>
       </c>
@@ -6707,7 +6776,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>48</v>
       </c>
@@ -6727,7 +6796,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -6747,27 +6816,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A144" t="s">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="F144" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F144" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>185</v>
       </c>
@@ -6787,27 +6859,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A146" t="s">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="6" t="s">
         <v>719</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="F146" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F146" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>178</v>
       </c>
@@ -6827,7 +6902,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>249</v>
       </c>
@@ -6847,7 +6922,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -6867,7 +6942,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>21</v>
       </c>
@@ -6887,7 +6962,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>108</v>
       </c>
@@ -6907,7 +6982,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>167</v>
       </c>
@@ -6927,7 +7002,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>225</v>
       </c>
@@ -6947,7 +7022,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>67</v>
       </c>
@@ -6967,7 +7042,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>184</v>
       </c>
@@ -6987,67 +7062,76 @@
         <v>257</v>
       </c>
     </row>
-    <row r="156" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A156" s="5" t="s">
+    <row r="156" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C156" s="5" t="s">
+      <c r="C156" s="6" t="s">
         <v>772</v>
       </c>
-      <c r="D156" s="5" t="s">
+      <c r="D156" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="E156" s="5" t="s">
+      <c r="E156" s="6" t="s">
         <v>774</v>
       </c>
-      <c r="F156" s="5" t="s">
+      <c r="F156" s="6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A157" t="s">
+      <c r="G156" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D157" s="6" t="s">
         <v>775</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="F157" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A158" t="s">
+      <c r="F157" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="6" t="s">
         <v>778</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D158" s="6" t="s">
         <v>779</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="F158" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F158" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>160</v>
       </c>
@@ -7067,7 +7151,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>30</v>
       </c>
@@ -7087,7 +7171,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>23</v>
       </c>
@@ -7107,7 +7191,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>46</v>
       </c>
@@ -7127,7 +7211,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>9</v>
       </c>
@@ -7147,7 +7231,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>151</v>
       </c>
@@ -7167,7 +7251,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>115</v>
       </c>
@@ -7187,7 +7271,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>50</v>
       </c>
@@ -7207,7 +7291,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>150</v>
       </c>
@@ -7227,7 +7311,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>116</v>
       </c>
@@ -7247,7 +7331,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>229</v>
       </c>
@@ -7267,7 +7351,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -7287,7 +7371,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>174</v>
       </c>
@@ -7307,7 +7391,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>213</v>
       </c>
@@ -7327,7 +7411,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>196</v>
       </c>
@@ -7347,7 +7431,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>165</v>
       </c>
@@ -7367,7 +7451,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>110</v>
       </c>
@@ -7387,7 +7471,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>158</v>
       </c>
@@ -7407,7 +7491,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -7424,7 +7508,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>172</v>
       </c>
@@ -7444,7 +7528,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>128</v>
       </c>
@@ -7464,7 +7548,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>168</v>
       </c>
@@ -7484,7 +7568,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>37</v>
       </c>
@@ -7504,7 +7588,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>235</v>
       </c>
@@ -7524,7 +7608,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>248</v>
       </c>
@@ -7544,7 +7628,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>187</v>
       </c>
@@ -7564,7 +7648,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>96</v>
       </c>
@@ -7584,7 +7668,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>42</v>
       </c>
@@ -7604,27 +7688,30 @@
         <v>843</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A187" t="s">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="6" t="s">
         <v>844</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D187" s="6" t="s">
         <v>845</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="6" t="s">
         <v>846</v>
       </c>
-      <c r="F187" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F187" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>69</v>
       </c>
@@ -7644,7 +7731,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>177</v>
       </c>
@@ -7664,7 +7751,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>166</v>
       </c>
@@ -7684,7 +7771,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>157</v>
       </c>
@@ -7704,7 +7791,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>228</v>
       </c>
@@ -7724,7 +7811,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>153</v>
       </c>
@@ -7744,7 +7831,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>76</v>
       </c>
@@ -7764,7 +7851,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>64</v>
       </c>
@@ -7784,7 +7871,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>239</v>
       </c>
@@ -7804,27 +7891,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A197" t="s">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C197" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D197" s="6" t="s">
         <v>870</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="6" t="s">
         <v>872</v>
       </c>
-      <c r="F197" t="s">
+      <c r="F197" s="6" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="G197" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>156</v>
       </c>
@@ -7844,7 +7934,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>106</v>
       </c>
@@ -7864,7 +7954,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>125</v>
       </c>
@@ -7884,7 +7974,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>242</v>
       </c>
@@ -7904,7 +7994,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>101</v>
       </c>
@@ -7924,7 +8014,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>79</v>
       </c>
@@ -7944,7 +8034,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -7964,7 +8054,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>221</v>
       </c>
@@ -7984,7 +8074,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -8004,7 +8094,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>224</v>
       </c>
@@ -8024,27 +8114,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A208" t="s">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C208" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="D208" t="s">
+      <c r="D208" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E208" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="F208" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F208" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G208" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>14</v>
       </c>
@@ -8064,7 +8157,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>44</v>
       </c>
@@ -8084,7 +8177,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>75</v>
       </c>
@@ -8104,7 +8197,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>200</v>
       </c>
@@ -8124,24 +8217,28 @@
         <v>257</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A213" t="s">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C213" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="D213" t="s">
+      <c r="D213" s="6" t="s">
         <v>910</v>
       </c>
-      <c r="F213" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="E213" s="6"/>
+      <c r="F213" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G213" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>182</v>
       </c>
@@ -8161,27 +8258,30 @@
         <v>257</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A215" t="s">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C215" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="D215" t="s">
+      <c r="D215" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="E215" t="s">
+      <c r="E215" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="F215" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F215" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G215" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>197</v>
       </c>
@@ -8201,7 +8301,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>181</v>
       </c>
@@ -8221,7 +8321,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>122</v>
       </c>
@@ -8241,7 +8341,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>119</v>
       </c>
@@ -8261,7 +8361,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>155</v>
       </c>
@@ -8281,7 +8381,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>8</v>
       </c>
@@ -8301,7 +8401,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>215</v>
       </c>
@@ -8321,7 +8421,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>237</v>
       </c>
@@ -8341,7 +8441,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>58</v>
       </c>
@@ -8361,7 +8461,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>190</v>
       </c>
@@ -8381,7 +8481,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>199</v>
       </c>
@@ -8401,7 +8501,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>214</v>
       </c>
@@ -8421,7 +8521,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>62</v>
       </c>
@@ -8441,7 +8541,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>81</v>
       </c>
@@ -8461,7 +8561,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>136</v>
       </c>
@@ -8481,7 +8581,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>218</v>
       </c>
@@ -8501,7 +8601,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>206</v>
       </c>
@@ -8521,7 +8621,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>45</v>
       </c>
@@ -8541,7 +8641,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>140</v>
       </c>
@@ -8561,7 +8661,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>145</v>
       </c>
@@ -8581,7 +8681,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>25</v>
       </c>
@@ -8601,7 +8701,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>195</v>
       </c>
@@ -8621,7 +8721,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>227</v>
       </c>
@@ -8641,7 +8741,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>175</v>
       </c>
@@ -8661,7 +8761,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>188</v>
       </c>
@@ -8681,7 +8781,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>107</v>
       </c>
@@ -8701,7 +8801,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>164</v>
       </c>
@@ -8721,7 +8821,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>232</v>
       </c>
@@ -8741,7 +8841,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>171</v>
       </c>
@@ -8758,7 +8858,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>170</v>
       </c>
@@ -8778,7 +8878,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>220</v>
       </c>
@@ -8798,7 +8898,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>131</v>
       </c>
@@ -8818,7 +8918,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>163</v>
       </c>
@@ -8838,27 +8938,30 @@
         <v>456</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A249" t="s">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A249" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C249" t="s">
+      <c r="C249" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="D249" t="s">
+      <c r="D249" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="E249" t="s">
+      <c r="E249" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="F249" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="F249" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G249" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>147</v>
       </c>
@@ -8878,7 +8981,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>105</v>
       </c>
